--- a/artfynd/A 15142-2025 artfynd.xlsx
+++ b/artfynd/A 15142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91442972</v>
+        <v>91443190</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2223,14 +2223,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gravåsen (1), Mpd</t>
+          <t>Gravåsen (2), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594331</v>
+        <v>594246</v>
       </c>
       <c r="R15" t="n">
-        <v>6958315</v>
+        <v>6958314</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Y-Sun-0109</t>
+          <t>Y-Sun-0111</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2292,122 +2292,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>91443190</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98355</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gravåsen (2), Mpd</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>594246</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6958314</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Liden</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Y-Sun-0111</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 15142-2025 artfynd.xlsx
+++ b/artfynd/A 15142-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85437145</v>
+        <v>85437141</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594246.9379556014</v>
+        <v>594233</v>
       </c>
       <c r="R2" t="n">
-        <v>6958252.819392183</v>
+        <v>6958258</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85437139</v>
+        <v>85437145</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594214.9860152345</v>
+        <v>594247</v>
       </c>
       <c r="R3" t="n">
-        <v>6958310.14797219</v>
+        <v>6958253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85437142</v>
+        <v>85437144</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594233.0140224496</v>
+        <v>594247</v>
       </c>
       <c r="R4" t="n">
-        <v>6958257.924124737</v>
+        <v>6958253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85437144</v>
+        <v>85437149</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594246.9379556014</v>
+        <v>594353</v>
       </c>
       <c r="R5" t="n">
-        <v>6958252.819392183</v>
+        <v>6958363</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85437150</v>
+        <v>85437139</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594363.960468807</v>
+        <v>594215</v>
       </c>
       <c r="R6" t="n">
-        <v>6958368.071361044</v>
+        <v>6958310</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85437141</v>
+        <v>85437142</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594233.0140224496</v>
+        <v>594233</v>
       </c>
       <c r="R7" t="n">
-        <v>6958257.924124737</v>
+        <v>6958258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85437149</v>
+        <v>85437140</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594353.0789697436</v>
+        <v>594226</v>
       </c>
       <c r="R8" t="n">
-        <v>6958363.17347246</v>
+        <v>6958262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>85437140</v>
+        <v>85437146</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594226.0127241504</v>
+        <v>594324</v>
       </c>
       <c r="R9" t="n">
-        <v>6958261.851215295</v>
+        <v>6958256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1450,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>85437146</v>
+        <v>85437150</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594324.0042251089</v>
+        <v>594364</v>
       </c>
       <c r="R10" t="n">
-        <v>6958255.943891735</v>
+        <v>6958368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1551,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>85437151</v>
+        <v>85437143</v>
       </c>
       <c r="B11" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594363.960468807</v>
+        <v>594247</v>
       </c>
       <c r="R11" t="n">
-        <v>6958368.071361044</v>
+        <v>6958253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1652,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85437143</v>
+        <v>85437148</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594246.9379556014</v>
+        <v>594331</v>
       </c>
       <c r="R12" t="n">
-        <v>6958252.819392183</v>
+        <v>6958315</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1753,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,50 +1786,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>85437147</v>
+        <v>91443190</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gravåsen, Mpd</t>
+          <t>Gravåsen (2), Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594326.1535398229</v>
+        <v>594246</v>
       </c>
       <c r="R13" t="n">
-        <v>6958277.101575248</v>
+        <v>6958314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,39 +1853,35 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Y-Sun-0111</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2061,43 +1891,38 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering Y-län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85437148</v>
+        <v>85437147</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594331.0422554722</v>
+        <v>594326</v>
       </c>
       <c r="R14" t="n">
-        <v>6958314.847416529</v>
+        <v>6958277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1965,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,54 +1998,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91443190</v>
+        <v>85437151</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gravåsen (2), Mpd</t>
+          <t>Gravåsen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594246</v>
+        <v>594364</v>
       </c>
       <c r="R15" t="n">
-        <v>6958314</v>
+        <v>6958368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,11 +2061,6 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Y-Sun-0111</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>2020-05-13</t>
@@ -2276,14 +2077,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Åsa Michold</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2293,7 +2093,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15142-2025 artfynd.xlsx
+++ b/artfynd/A 15142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85437144</v>
+        <v>134786672</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594247</v>
+        <v>594372</v>
       </c>
       <c r="R4" t="n">
-        <v>6958253</v>
+        <v>6958229</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -942,12 +942,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,26 +972,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85437149</v>
+        <v>134786687</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,13 +1019,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594353</v>
+        <v>594304</v>
       </c>
       <c r="R5" t="n">
-        <v>6958363</v>
+        <v>6958287</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1043,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,26 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85437139</v>
+        <v>134786692</v>
       </c>
       <c r="B6" t="n">
-        <v>92369</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1126,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594215</v>
+        <v>594267</v>
       </c>
       <c r="R6" t="n">
-        <v>6958310</v>
+        <v>6958303</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1144,12 +1156,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,26 +1186,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85437142</v>
+        <v>134786693</v>
       </c>
       <c r="B7" t="n">
-        <v>92369</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,13 +1233,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594233</v>
+        <v>594286</v>
       </c>
       <c r="R7" t="n">
-        <v>6958258</v>
+        <v>6958313</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1263,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,26 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85437140</v>
+        <v>134786706</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,13 +1340,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594226</v>
+        <v>594316</v>
       </c>
       <c r="R8" t="n">
-        <v>6958262</v>
+        <v>6958369</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1346,12 +1370,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1366,26 +1400,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>85437146</v>
+        <v>134786710</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594324</v>
+        <v>594288</v>
       </c>
       <c r="R9" t="n">
-        <v>6958256</v>
+        <v>6958373</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,12 +1477,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1467,48 +1507,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>85437150</v>
+        <v>134786728</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,13 +1554,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594364</v>
+        <v>594201</v>
       </c>
       <c r="R10" t="n">
-        <v>6958368</v>
+        <v>6958386</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,12 +1584,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,48 +1614,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>85437143</v>
+        <v>134786731</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,13 +1661,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594247</v>
+        <v>594220</v>
       </c>
       <c r="R11" t="n">
-        <v>6958253</v>
+        <v>6958396</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1649,12 +1691,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,26 +1721,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85437148</v>
+        <v>134786690</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>92689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1744,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,13 +1768,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594331</v>
+        <v>594278</v>
       </c>
       <c r="R12" t="n">
-        <v>6958315</v>
+        <v>6958305</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1750,12 +1798,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,65 +1828,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Michold</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91443190</v>
+        <v>85437144</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gravåsen (2), Mpd</t>
+          <t>Gravåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594246</v>
+        <v>594247</v>
       </c>
       <c r="R13" t="n">
-        <v>6958314</v>
+        <v>6958253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1903,6 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Y-Sun-0111</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>2020-05-13</t>
@@ -1874,14 +1919,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Åsa Michold</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -1891,38 +1935,38 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85437147</v>
+        <v>85437149</v>
       </c>
       <c r="B14" t="n">
-        <v>80392</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594326</v>
+        <v>594353</v>
       </c>
       <c r="R14" t="n">
-        <v>6958277</v>
+        <v>6958363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +2042,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>85437151</v>
+        <v>134786682</v>
       </c>
       <c r="B15" t="n">
-        <v>80392</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,13 +2077,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594364</v>
+        <v>594320</v>
       </c>
       <c r="R15" t="n">
-        <v>6958368</v>
+        <v>6958257</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2063,12 +2107,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,19 +2137,6176 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134786713</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594287</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6958379</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134786727</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6958385</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134786730</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>594202</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6958392</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>85437139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594215</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6958310</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Åsa Michold</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Åsa Michold</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>85437142</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>594233</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6958258</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134786673</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594368</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6958226</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134786691</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>594279</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6958303</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134786694</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>594287</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6958313</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134786696</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594327</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6958302</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134786714</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594290</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6958385</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134786729</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>594204</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6958385</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>85437140</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>594226</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6958262</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134786700</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>594393</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6958265</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134786675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>594360</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6958230</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134786705</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>594360</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6958404</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134786720</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>594262</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6958391</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134786695</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>594328</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6958306</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134786697</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>594362</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6958271</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134786698</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>594367</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6958269</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134786704</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>594398</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6958363</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134786716</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>594282</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6958399</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134786676</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>594367</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6958238</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134786677</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>594366</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6958241</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134786732</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>594258</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6958369</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>85437146</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>594324</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6958256</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134786686</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>594320</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6958280</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134786688</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>594304</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6958288</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134786723</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>594216</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6958422</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>85437150</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>594364</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6958368</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134786678</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>594367</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6958242</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134786684</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>594317</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6958276</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134786709</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>594292</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6958370</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134786679</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>594367</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6958240</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134786681</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>594326</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6958256</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134786733</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>594254</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6958369</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134786735</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>594270</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6958335</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134786699</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>594383</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6958265</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134786701</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>594374</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6958289</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Många ringhack som går högt upp på stammen</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134786702</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>594420</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6958307</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134786718</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>594259</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6958386</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134786726</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>594196</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6958382</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>85437143</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>594247</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6958253</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>85437148</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>594331</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6958315</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>91443190</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gravåsen (2), Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>594246</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6958314</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Y-Sun-0111</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134786703</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>594429</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6958339</v>
+      </c>
+      <c r="S60" t="n">
+        <v>9</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>30 ex</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134786707</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>594305</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6958360</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>20 ex</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134786708</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>594302</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6958361</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>145 ex</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134786711</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>594285</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6958375</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>20 ex</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134786715</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>594283</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6958398</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134786717</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>594259</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6958390</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>50 ex</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134786724</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>594202</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6958425</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>90 ex</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134786725</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99232</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>594180</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6958430</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>85437147</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>594326</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6958277</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>85437151</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>594364</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6958368</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134786683</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>594313</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6958260</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134786685</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>594319</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6958278</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134786689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gravåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>594300</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6958296</v>
+      </c>
+      <c r="S72" t="n">
+        <v>6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15142-2025 artfynd.xlsx
+++ b/artfynd/A 15142-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437141</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786687</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786692</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786693</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786710</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786728</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786731</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786690</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437144</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437149</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786682</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786713</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786727</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786730</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,6 +2764,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437142</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2776,6 +2876,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786673</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786691</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786694</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3097,6 +3212,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786696</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3204,6 +3324,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786714</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3311,6 +3436,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786729</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3412,6 +3542,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437140</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3519,6 +3654,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786700</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3626,6 +3766,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786675</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3733,6 +3878,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786705</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3840,6 +3990,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786720</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3947,6 +4102,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786695</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4054,6 +4214,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786697</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786698</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4268,6 +4438,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786704</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4375,6 +4550,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786716</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4482,6 +4662,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786676</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4589,6 +4774,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786677</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4696,6 +4886,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786732</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4797,6 +4992,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437146</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4904,6 +5104,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786686</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5011,6 +5216,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786688</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5118,6 +5328,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786723</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5219,6 +5434,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437150</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5326,6 +5546,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786678</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5433,6 +5658,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786684</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5540,6 +5770,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786709</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5647,6 +5882,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786679</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5754,6 +5994,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786681</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5861,6 +6106,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786733</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5980,6 +6230,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786735</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6100,6 +6355,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786699</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6220,6 +6480,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786701</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6340,6 +6605,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786702</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6460,6 +6730,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786718</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6580,6 +6855,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786726</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6681,6 +6961,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437143</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6780,6 +7065,11 @@
       <c r="AY58" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437148</t>
         </is>
       </c>
     </row>
@@ -6893,6 +7183,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91443190</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7005,6 +7300,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786703</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7117,6 +7417,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786707</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7229,6 +7534,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786708</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7341,6 +7651,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786711</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7453,6 +7768,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786715</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7565,6 +7885,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786717</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7677,6 +8002,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786724</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7784,6 +8114,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786725</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7885,6 +8220,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437147</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7986,6 +8326,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85437151</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8093,6 +8438,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786683</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8200,6 +8550,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786685</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8307,8 +8662,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134786689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>